--- a/data/trans_dic/POLIPATOLOGIA_Lim_5-Edad-trans_dic.xlsx
+++ b/data/trans_dic/POLIPATOLOGIA_Lim_5-Edad-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con cinco o más enfermedades crónicas de las que al menos una es limitante</t>
+          <t>Población con cinco o más enfermedades crónicas de las que al menos una es limitante (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,09</t>
+          <t>0,0; 1,06</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,11</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,45</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,21</t>
+          <t>0,0; 1,22</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,52; 5,65</t>
+          <t>0,53; 5,8</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,6</t>
+          <t>0,0; 0,51</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,59</t>
+          <t>0,0; 0,71</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,52</t>
+          <t>0,22; 2,44</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,29</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,34</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,92</t>
+          <t>0,0; 2,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,44; 2,51</t>
+          <t>0,45; 2,65</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,4; 2,19</t>
+          <t>0,36; 2,36</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,19; 4,33</t>
+          <t>1,26; 4,48</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,21; 1,33</t>
+          <t>0,21; 1,17</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,11</t>
+          <t>0,2; 1,13</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,86; 2,62</t>
+          <t>0,91; 2,63</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,18</t>
+          <t>0,13; 1,34</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,35</t>
+          <t>0,0; 1,28</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,84; 5,07</t>
+          <t>1,84; 4,91</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,76; 4,25</t>
+          <t>1,79; 4,36</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,25; 3,38</t>
+          <t>1,28; 3,58</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,71; 5,67</t>
+          <t>2,73; 5,67</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,06; 2,58</t>
+          <t>1,08; 2,41</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,81; 2,02</t>
+          <t>0,79; 1,95</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,62; 4,89</t>
+          <t>2,7; 4,83</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,04; 3,94</t>
+          <t>1,19; 3,72</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,19; 3,67</t>
+          <t>1,21; 3,57</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,78; 6,68</t>
+          <t>1,76; 6,68</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,08; 8,05</t>
+          <t>3,9; 8,14</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,27; 7,99</t>
+          <t>4,22; 7,9</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,56; 14,61</t>
+          <t>9,7; 14,62</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,96; 5,34</t>
+          <t>2,91; 5,35</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,05; 5,33</t>
+          <t>3,12; 5,42</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,5; 9,72</t>
+          <t>4,71; 9,83</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,95; 5,6</t>
+          <t>1,92; 5,35</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,22; 7,61</t>
+          <t>3,1; 7,61</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,74; 11,2</t>
+          <t>6,8; 11,02</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11,52; 18,56</t>
+          <t>11,36; 18,4</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>11,77; 18,68</t>
+          <t>11,82; 18,33</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,66; 20,36</t>
+          <t>15,63; 20,38</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,24; 11,32</t>
+          <t>7,46; 11,57</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>8,25; 12,52</t>
+          <t>8,19; 12,22</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>11,62; 14,99</t>
+          <t>11,82; 15,21</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9,92; 18,1</t>
+          <t>9,71; 17,87</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4,37; 9,79</t>
+          <t>4,12; 9,4</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10,56; 15,86</t>
+          <t>10,33; 15,84</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>15,22; 23,76</t>
+          <t>15,08; 23,62</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>16,86; 25,4</t>
+          <t>16,91; 25,58</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,72; 26,02</t>
+          <t>7,67; 26,2</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>13,57; 19,61</t>
+          <t>13,89; 19,62</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>11,64; 16,74</t>
+          <t>11,82; 17,32</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>8,67; 20,21</t>
+          <t>8,08; 20,09</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>15,14; 25,3</t>
+          <t>15,19; 26,21</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>12,58; 20,98</t>
+          <t>13,18; 22,2</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>23,48; 31,5</t>
+          <t>23,11; 31,39</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>29,52; 39,22</t>
+          <t>29,15; 39,33</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>21,35; 31,2</t>
+          <t>21,34; 30,64</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>41,07; 47,8</t>
+          <t>41,21; 48,02</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>25,23; 32,4</t>
+          <t>24,97; 32,41</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>19,01; 25,9</t>
+          <t>19,21; 25,89</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>35,11; 40,38</t>
+          <t>35,09; 40,3</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,91; 4,25</t>
+          <t>2,92; 4,31</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,53; 3,75</t>
+          <t>2,59; 3,76</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5,16; 7,57</t>
+          <t>5,17; 7,62</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8,24; 10,3</t>
+          <t>8,33; 10,28</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>7,94; 10,05</t>
+          <t>8,03; 10,11</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,25; 15,3</t>
+          <t>11,13; 15,28</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,86; 7,09</t>
+          <t>5,88; 7,06</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>5,49; 6,66</t>
+          <t>5,52; 6,69</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>9,1; 11,33</t>
+          <t>9,07; 11,41</t>
         </is>
       </c>
     </row>
@@ -1543,7 +1543,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con cinco o más enfermedades crónicas de las que al menos una es limitante</t>
+          <t>Población con cinco o más enfermedades crónicas de las que al menos una es limitante (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1750,47 +1750,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4969</t>
+          <t>0; 4825</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 2044</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 4435</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 1957</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 4806</t>
+          <t>0; 4843</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1629; 17697</t>
+          <t>1671; 18179</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 5326</t>
+          <t>0; 4503</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 4815</t>
+          <t>0; 5775</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1645; 17963</t>
+          <t>1584; 17421</t>
         </is>
       </c>
     </row>
@@ -1913,47 +1913,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 1975</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 1996</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 8145</t>
+          <t>0; 8463</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2689; 15343</t>
+          <t>2731; 16171</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2270; 12340</t>
+          <t>2033; 13299</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6097; 22155</t>
+          <t>6455; 22940</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2767; 17224</t>
+          <t>2746; 15178</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1934; 12807</t>
+          <t>2349; 12997</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8022; 24473</t>
+          <t>8493; 24621</t>
         </is>
       </c>
     </row>
@@ -2076,47 +2076,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>889; 8022</t>
+          <t>887; 9137</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 9025</t>
+          <t>0; 8560</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9863; 27171</t>
+          <t>9874; 26332</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12477; 30219</t>
+          <t>12743; 30969</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>8259; 22322</t>
+          <t>8485; 23650</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16015; 33577</t>
+          <t>16176; 33541</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14702; 35878</t>
+          <t>15000; 33498</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>10713; 26833</t>
+          <t>10565; 25990</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>29530; 55142</t>
+          <t>30509; 54495</t>
         </is>
       </c>
     </row>
@@ -2239,47 +2239,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6421; 24205</t>
+          <t>7327; 22845</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7696; 23708</t>
+          <t>7806; 23093</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15840; 59347</t>
+          <t>15665; 59337</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>25166; 49575</t>
+          <t>24047; 50163</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>27684; 51892</t>
+          <t>27385; 51300</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>68183; 104117</t>
+          <t>69142; 104223</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>36391; 65714</t>
+          <t>35826; 65876</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>39509; 69032</t>
+          <t>40379; 70149</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>72006; 155593</t>
+          <t>75462; 157339</t>
         </is>
       </c>
     </row>
@@ -2402,47 +2402,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>8359; 24046</t>
+          <t>8253; 22983</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>15403; 36346</t>
+          <t>14792; 36376</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>37807; 62866</t>
+          <t>38160; 61842</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>51574; 83126</t>
+          <t>50869; 82418</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>58494; 92805</t>
+          <t>58712; 91067</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>85829; 111534</t>
+          <t>85655; 111684</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>63521; 99289</t>
+          <t>65447; 101479</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>80383; 122035</t>
+          <t>79805; 119098</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>128841; 166207</t>
+          <t>131118; 168736</t>
         </is>
       </c>
     </row>
@@ -2565,47 +2565,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>30725; 56071</t>
+          <t>30081; 55354</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>14623; 32719</t>
+          <t>13774; 31424</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>38893; 58400</t>
+          <t>38016; 58322</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>53870; 84119</t>
+          <t>53374; 83617</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>63672; 95948</t>
+          <t>63864; 96629</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>40874; 158279</t>
+          <t>46679; 159381</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>90081; 130167</t>
+          <t>92178; 130225</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>82883; 119187</t>
+          <t>84144; 123311</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>84701; 197334</t>
+          <t>78920; 196155</t>
         </is>
       </c>
     </row>
@@ -2728,47 +2728,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>37837; 63213</t>
+          <t>37953; 65489</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>32334; 53918</t>
+          <t>33876; 57057</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>66398; 89078</t>
+          <t>65343; 88769</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>114831; 152571</t>
+          <t>113395; 152991</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>85426; 124838</t>
+          <t>85410; 122609</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>174891; 203555</t>
+          <t>175496; 204494</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>161168; 207006</t>
+          <t>159519; 207014</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>124918; 170201</t>
+          <t>126212; 170137</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>248792; 286108</t>
+          <t>248671; 285532</t>
         </is>
       </c>
     </row>
@@ -2891,47 +2891,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>99877; 145479</t>
+          <t>99908; 147553</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>85975; 127247</t>
+          <t>87899; 127715</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>178594; 261829</t>
+          <t>178838; 263678</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>293090; 366377</t>
+          <t>296365; 365898</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>281573; 356245</t>
+          <t>284649; 358179</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>417804; 567954</t>
+          <t>413012; 567137</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>409542; 495356</t>
+          <t>410937; 492949</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>380773; 462015</t>
+          <t>382863; 464351</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>652587; 812477</t>
+          <t>650438; 818617</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/POLIPATOLOGIA_Lim_5-Edad-trans_dic.xlsx
+++ b/data/trans_dic/POLIPATOLOGIA_Lim_5-Edad-trans_dic.xlsx
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,87%</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,06</t>
+          <t>0,0; 0,95</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -698,27 +698,27 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,22</t>
+          <t>0,0; 1,26</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,53; 5,8</t>
+          <t>0,56; 5,2</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,51</t>
+          <t>0,0; 0,55</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,71</t>
+          <t>0,0; 0,7</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,22; 2,44</t>
+          <t>0,26; 2,29</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,71%</t>
         </is>
       </c>
     </row>
@@ -798,37 +798,37 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,0</t>
+          <t>0,0; 1,97</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,45; 2,65</t>
+          <t>0,47; 2,52</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,36; 2,36</t>
+          <t>0,48; 2,36</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,26; 4,48</t>
+          <t>1,6; 4,47</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,21; 1,17</t>
+          <t>0,21; 1,27</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,13</t>
+          <t>0,2; 1,12</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,91; 2,63</t>
+          <t>1,01; 2,71</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,66%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,34</t>
+          <t>0,13; 1,37</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,28</t>
+          <t>0,0; 1,19</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,84; 4,91</t>
+          <t>1,61; 4,62</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,79; 4,36</t>
+          <t>1,67; 4,28</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,28; 3,58</t>
+          <t>1,27; 3,53</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,73; 5,67</t>
+          <t>3,1; 5,95</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,08; 2,41</t>
+          <t>1,05; 2,41</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,79; 1,95</t>
+          <t>0,8; 2,08</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,7; 4,83</t>
+          <t>2,71; 4,74</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>8,77%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,19; 3,72</t>
+          <t>1,07; 3,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,21; 3,57</t>
+          <t>1,24; 3,67</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,76; 6,68</t>
+          <t>4,15; 7,87</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,9; 8,14</t>
+          <t>4,23; 8,31</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,22; 7,9</t>
+          <t>4,18; 7,98</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,7; 14,62</t>
+          <t>9,96; 13,7</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,91; 5,35</t>
+          <t>2,89; 5,31</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,12; 5,42</t>
+          <t>3,13; 5,27</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,71; 9,83</t>
+          <t>7,5; 10,17</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,17%</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,92; 5,35</t>
+          <t>1,88; 5,47</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,1; 7,61</t>
+          <t>3,07; 7,52</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,8; 11,02</t>
+          <t>6,71; 10,93</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11,36; 18,4</t>
+          <t>11,48; 18,32</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>11,82; 18,33</t>
+          <t>11,88; 18,42</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,63; 20,38</t>
+          <t>15,3; 20,26</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,46; 11,57</t>
+          <t>7,36; 11,35</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>8,19; 12,22</t>
+          <t>8,09; 12,3</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>11,82; 15,21</t>
+          <t>11,62; 14,86</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>19,1%</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9,71; 17,87</t>
+          <t>9,61; 18,42</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4,12; 9,4</t>
+          <t>4,21; 10,13</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10,33; 15,84</t>
+          <t>9,59; 14,85</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>15,08; 23,62</t>
+          <t>14,91; 23,35</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>16,91; 25,58</t>
+          <t>16,56; 25,6</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7,67; 26,2</t>
+          <t>22,7; 28,92</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>13,89; 19,62</t>
+          <t>13,71; 19,88</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>11,82; 17,32</t>
+          <t>11,61; 16,88</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>8,08; 20,09</t>
+          <t>17,1; 21,15</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>44,49%</t>
+          <t>44,5%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>37,58%</t>
+          <t>37,59%</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>15,19; 26,21</t>
+          <t>14,75; 24,99</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>13,18; 22,2</t>
+          <t>13,05; 21,47</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>23,11; 31,39</t>
+          <t>23,24; 31,51</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>29,15; 39,33</t>
+          <t>29,35; 39,13</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>21,34; 30,64</t>
+          <t>20,96; 30,99</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>41,21; 48,02</t>
+          <t>40,93; 47,85</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>24,97; 32,41</t>
+          <t>24,75; 32,05</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>19,21; 25,89</t>
+          <t>19,25; 26,21</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>35,09; 40,3</t>
+          <t>34,86; 40,34</t>
         </is>
       </c>
     </row>
@@ -1405,7 +1405,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>11,12%</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,92; 4,31</t>
+          <t>2,95; 4,36</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,59; 3,76</t>
+          <t>2,51; 3,81</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5,17; 7,62</t>
+          <t>6,2; 7,73</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8,33; 10,28</t>
+          <t>8,36; 10,44</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>8,03; 10,11</t>
+          <t>7,95; 10,02</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,13; 15,28</t>
+          <t>14,09; 15,98</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,88; 7,06</t>
+          <t>5,9; 7,12</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>5,52; 6,69</t>
+          <t>5,52; 6,72</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>9,07; 11,41</t>
+          <t>10,49; 11,77</t>
         </is>
       </c>
     </row>
@@ -1722,7 +1722,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6370</t>
+          <t>6700</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6370</t>
+          <t>6700</t>
         </is>
       </c>
     </row>
@@ -1750,7 +1750,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4825</t>
+          <t>0; 4298</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1770,27 +1770,27 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 4843</t>
+          <t>0; 4986</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1671; 18179</t>
+          <t>2047; 18843</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 4503</t>
+          <t>0; 4830</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 5775</t>
+          <t>0; 5708</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1584; 17421</t>
+          <t>2037; 17642</t>
         </is>
       </c>
     </row>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2397</t>
+          <t>2566</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1885,7 +1885,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>12805</t>
+          <t>14131</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>15203</t>
+          <t>16698</t>
         </is>
       </c>
     </row>
@@ -1923,37 +1923,37 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 8463</t>
+          <t>0; 9408</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2731; 16171</t>
+          <t>2883; 15383</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2033; 13299</t>
+          <t>2680; 13276</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6455; 22940</t>
+          <t>8039; 22417</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2746; 15178</t>
+          <t>2775; 16464</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2349; 12997</t>
+          <t>2277; 12893</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8493; 24621</t>
+          <t>9893; 26534</t>
         </is>
       </c>
     </row>
@@ -2033,7 +2033,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16617</t>
+          <t>17639</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24180</t>
+          <t>27954</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>40798</t>
+          <t>45592</t>
         </is>
       </c>
     </row>
@@ -2076,47 +2076,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>887; 9137</t>
+          <t>912; 9311</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 8560</t>
+          <t>0; 7932</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9874; 26332</t>
+          <t>9986; 28684</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12743; 30969</t>
+          <t>11870; 30409</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>8485; 23650</t>
+          <t>8398; 23373</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16176; 33541</t>
+          <t>19312; 37055</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15000; 33498</t>
+          <t>14581; 33521</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>10565; 25990</t>
+          <t>10688; 27686</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>30509; 54495</t>
+          <t>33773; 59019</t>
         </is>
       </c>
     </row>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>37920</t>
+          <t>40086</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85433</t>
+          <t>85972</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>123353</t>
+          <t>126058</t>
         </is>
       </c>
     </row>
@@ -2239,47 +2239,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7327; 22845</t>
+          <t>6549; 22595</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7806; 23093</t>
+          <t>8016; 23686</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15665; 59337</t>
+          <t>29095; 55120</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>24047; 50163</t>
+          <t>26076; 51178</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>27385; 51300</t>
+          <t>27151; 51787</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>69142; 104223</t>
+          <t>73426; 100932</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>35826; 65876</t>
+          <t>35566; 65365</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>40379; 70149</t>
+          <t>40524; 68219</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>75462; 157339</t>
+          <t>107876; 146253</t>
         </is>
       </c>
     </row>
@@ -2359,7 +2359,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>49327</t>
+          <t>52449</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97828</t>
+          <t>108007</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>147156</t>
+          <t>160456</t>
         </is>
       </c>
     </row>
@@ -2402,47 +2402,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>8253; 22983</t>
+          <t>8092; 23499</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>14792; 36376</t>
+          <t>14650; 35916</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>38160; 61842</t>
+          <t>40913; 66622</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>50869; 82418</t>
+          <t>51400; 82015</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>58712; 91067</t>
+          <t>59017; 91530</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>85655; 111684</t>
+          <t>93154; 123383</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>65447; 101479</t>
+          <t>64602; 99576</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>79805; 119098</t>
+          <t>78882; 119925</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>131118; 168736</t>
+          <t>141566; 181060</t>
         </is>
       </c>
     </row>
@@ -2522,7 +2522,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>47468</t>
+          <t>49488</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>101504</t>
+          <t>112134</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2552,7 +2552,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>148972</t>
+          <t>161621</t>
         </is>
       </c>
     </row>
@@ -2565,47 +2565,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>30081; 55354</t>
+          <t>29758; 57048</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>13774; 31424</t>
+          <t>14071; 33862</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>38016; 58322</t>
+          <t>39043; 60453</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>53374; 83617</t>
+          <t>52770; 82668</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>63864; 96629</t>
+          <t>62549; 96711</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>46679; 159381</t>
+          <t>99688; 127011</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>92178; 130225</t>
+          <t>91015; 131983</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>84144; 123311</t>
+          <t>82673; 120230</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>78920; 196155</t>
+          <t>144711; 179012</t>
         </is>
       </c>
     </row>
@@ -2685,7 +2685,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>76801</t>
+          <t>84473</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>189473</t>
+          <t>206769</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>266274</t>
+          <t>291242</t>
         </is>
       </c>
     </row>
@@ -2728,47 +2728,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>37953; 65489</t>
+          <t>36863; 62434</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>33876; 57057</t>
+          <t>33537; 55168</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>65343; 88769</t>
+          <t>72076; 97743</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>113395; 152991</t>
+          <t>114178; 152218</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>85410; 122609</t>
+          <t>83861; 124006</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>175496; 204494</t>
+          <t>190145; 222307</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>159519; 207014</t>
+          <t>158123; 204742</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>126212; 170137</t>
+          <t>126479; 172265</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>248671; 285532</t>
+          <t>270078; 312583</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>230531</t>
+          <t>246701</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -2863,7 +2863,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>517594</t>
+          <t>561666</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>748125</t>
+          <t>808367</t>
         </is>
       </c>
     </row>
@@ -2891,47 +2891,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>99908; 147553</t>
+          <t>101165; 149257</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>87899; 127715</t>
+          <t>85097; 129311</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>178838; 263678</t>
+          <t>219051; 273162</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>296365; 365898</t>
+          <t>297365; 371449</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>284649; 358179</t>
+          <t>281670; 355091</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>413012; 567137</t>
+          <t>526629; 597294</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>410937; 492949</t>
+          <t>412347; 497420</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>382863; 464351</t>
+          <t>383156; 466397</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>650438; 818617</t>
+          <t>762491; 855960</t>
         </is>
       </c>
     </row>
